--- a/Spine_Projects/01_input_data/01_input_raw/Products/hydrogen/Model_Data_Base_hydrogen.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/hydrogen/Model_Data_Base_hydrogen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/djh_eco_cbs_dk/Documents/Documents/GitHub/Nord_H2ub/Spine_Projects/01_input_data/01_input_raw/Products/hydrogen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{B63BCB0A-9012-4F55-92B6-F45564B797E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA6FC5F6-9826-47A8-8C2B-FE392B4B1DCE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7EAECE5-810D-4BEF-BA0F-CAD7C228B195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11730" yWindow="-21720" windowWidth="51840" windowHeight="21240" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="108">
   <si>
     <t>Unit</t>
   </si>
@@ -371,6 +371,33 @@
   </si>
   <si>
     <t>water_source</t>
+  </si>
+  <si>
+    <t>solar_plant_node</t>
+  </si>
+  <si>
+    <t>wind_onshore_plant_node</t>
+  </si>
+  <si>
+    <t>wind_offshore_plant_node</t>
+  </si>
+  <si>
+    <t>pl_wholesale_solar</t>
+  </si>
+  <si>
+    <t>pl_solar_PPA</t>
+  </si>
+  <si>
+    <t>pl_wholesale_wind_onshore</t>
+  </si>
+  <si>
+    <t>pl_wind_onshore_PPA</t>
+  </si>
+  <si>
+    <t>pl_wholesale_wind_offshore</t>
+  </si>
+  <si>
+    <t>pl_wind_offshore_PPA</t>
   </si>
 </sst>
 </file>
@@ -461,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -475,14 +502,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -493,6 +519,9 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1254,8 +1283,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA5" totalsRowShown="0">
-  <autoFilter ref="A1:AA5" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA11" totalsRowShown="0">
+  <autoFilter ref="A1:AA11" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{26B0CA71-1EA9-44CF-8E6D-31054ECA99A6}" name="Connection"/>
     <tableColumn id="26" xr3:uid="{E67F4435-EF76-417C-B715-53719E5FB41F}" name="Object_type"/>
@@ -1263,7 +1292,7 @@
     <tableColumn id="3" xr3:uid="{0B221EED-10BC-4C34-AC5E-37A826B1E8AE}" name="Input2"/>
     <tableColumn id="4" xr3:uid="{13095F0A-BCF6-40A3-B029-60B11214B154}" name="Output1"/>
     <tableColumn id="5" xr3:uid="{4C6B3E52-C4A2-4D67-B50B-9DAA089E0399}" name="Output2"/>
-    <tableColumn id="22" xr3:uid="{551A8663-4680-4147-9E64-4B9A8EA76642}" name="Connection_type" dataDxfId="2"/>
+    <tableColumn id="22" xr3:uid="{551A8663-4680-4147-9E64-4B9A8EA76642}" name="Connection_type" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{5DF4D35D-AD4C-4648-BC90-B2BA8F975A09}" name="Cap_Input1_existing"/>
     <tableColumn id="15" xr3:uid="{C0BCA9EF-0E20-40E5-9820-0EA6AB1DE457}" name="Cap_Input1_max"/>
     <tableColumn id="14" xr3:uid="{D4F16D16-99DE-47DA-B08A-6DD56FEBC7A4}" name="Cap_Input2_existing"/>
@@ -1282,7 +1311,7 @@
     <tableColumn id="21" xr3:uid="{EC2CC790-C17D-4744-A981-3984808E5B33}" name="vom_cost_Input2"/>
     <tableColumn id="24" xr3:uid="{41B338E4-2058-41E9-8000-97D77450FBC3}" name="vom_cost_Output1"/>
     <tableColumn id="25" xr3:uid="{DDAFCF0A-1EF1-4B7B-9742-01F9FA7A22E5}" name="vom_cost_Output2"/>
-    <tableColumn id="29" xr3:uid="{79DE3A19-CED6-47DE-AEF5-F6BB2D320F24}" name="connection_investment_tech_lifetime" dataDxfId="1"/>
+    <tableColumn id="29" xr3:uid="{79DE3A19-CED6-47DE-AEF5-F6BB2D320F24}" name="connection_investment_tech_lifetime" dataDxfId="0"/>
     <tableColumn id="30" xr3:uid="{09434E4A-7BF5-4547-9708-EA3F0F7ADC8E}" name="initial_connections_invested_available"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1293,8 +1322,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}" name="Table134" displayName="Table134" ref="A1:K5" totalsRowShown="0">
   <autoFilter ref="A1:K5" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="0">
-      <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Connections!A2:A100,ISNUMBER(FIND("storage",Connections!A2:A100)))</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="2">
+      <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Connections!A2:A105,ISNUMBER(FIND("storage",Connections!A2:A105)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{8C29206C-8DC6-44DB-A8D1-3D5625C277AD}" name="Object_type"/>
     <tableColumn id="4" xr3:uid="{AEAA1B51-84C1-491F-81D5-7757B30BDCCD}" name="value_before"/>
@@ -1619,14 +1648,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
   <dimension ref="A1:R11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.81640625" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="18" width="10.54296875" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="18" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1682,7 +1711,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -1690,12 +1719,12 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -1703,12 +1732,12 @@
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -1716,12 +1745,12 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -1743,7 +1772,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>97</v>
       </c>
@@ -1756,7 +1785,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>76</v>
       </c>
@@ -1769,26 +1798,26 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P9" s="1"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P9:P11 P2:P8" xr:uid="{D92CB468-B7A9-4082-9B81-D3B4634F286E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P11" xr:uid="{D92CB468-B7A9-4082-9B81-D3B4634F286E}">
       <formula1>"h, D, W, M, Q, Y"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1815,14 +1844,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CABA7C5-6230-4207-9D35-0A95D86E66AC}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-    <col min="2" max="2" width="13.26953125" customWidth="1"/>
-    <col min="7" max="8" width="9.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="7" max="8" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1875,7 +1904,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>62</v>
       </c>
@@ -1886,8 +1915,8 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="3" t="s">
-        <v>63</v>
+      <c r="G2" t="s">
+        <v>99</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="7"/>
@@ -1900,7 +1929,7 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>91</v>
       </c>
@@ -1911,8 +1940,8 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>63</v>
+      <c r="G3" t="s">
+        <v>100</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -1925,7 +1954,7 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -1936,8 +1965,8 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>63</v>
+      <c r="G4" t="s">
+        <v>101</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -1950,7 +1979,7 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>72</v>
       </c>
@@ -1985,7 +2014,7 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>76</v>
       </c>
@@ -2016,7 +2045,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>97</v>
       </c>
@@ -2045,7 +2074,7 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2064,7 +2093,7 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2083,7 +2112,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -2125,34 +2154,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C870BDA0-9E4C-481D-87BE-9D47789809C8}">
-  <dimension ref="A1:AA4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AA11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <col min="3" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.26953125" customWidth="1"/>
-    <col min="9" max="9" width="17.453125" customWidth="1"/>
-    <col min="10" max="10" width="15.453125" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.453125" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" customWidth="1"/>
     <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
     <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="10.54296875" customWidth="1"/>
-    <col min="17" max="17" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.81640625" customWidth="1"/>
-    <col min="21" max="21" width="12.81640625" customWidth="1"/>
-    <col min="22" max="23" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="35.26953125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.85546875" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" customWidth="1"/>
+    <col min="22" max="23" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -2235,7 +2264,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -2294,7 +2323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -2350,7 +2379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -2387,6 +2416,301 @@
       <c r="AA4">
         <v>1</v>
       </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5">
+        <v>1000</v>
+      </c>
+      <c r="I5">
+        <v>1000</v>
+      </c>
+      <c r="J5">
+        <v>1000</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
+      <c r="L5">
+        <v>1000</v>
+      </c>
+      <c r="M5">
+        <v>1000</v>
+      </c>
+      <c r="N5">
+        <v>1000</v>
+      </c>
+      <c r="O5">
+        <v>1000</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6">
+        <v>1000</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="L6">
+        <v>1000</v>
+      </c>
+      <c r="M6">
+        <v>1000</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>1000</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1000</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>1000</v>
+      </c>
+      <c r="M7">
+        <v>1000</v>
+      </c>
+      <c r="N7">
+        <v>1000</v>
+      </c>
+      <c r="O7">
+        <v>1000</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8">
+        <v>1000</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="L8">
+        <v>1000</v>
+      </c>
+      <c r="M8">
+        <v>1000</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9">
+        <v>1000</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9">
+        <v>1000</v>
+      </c>
+      <c r="K9">
+        <v>1000</v>
+      </c>
+      <c r="L9">
+        <v>1000</v>
+      </c>
+      <c r="M9">
+        <v>1000</v>
+      </c>
+      <c r="N9">
+        <v>1000</v>
+      </c>
+      <c r="O9">
+        <v>1000</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10">
+        <v>1000</v>
+      </c>
+      <c r="I10">
+        <v>1000</v>
+      </c>
+      <c r="L10">
+        <v>1000</v>
+      </c>
+      <c r="M10">
+        <v>1000</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="G11" s="9"/>
+      <c r="Z11" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2402,7 +2726,7 @@
           <x14:formula1>
             <xm:f>Drop_Down!$A$2:$A$60</xm:f>
           </x14:formula1>
-          <xm:sqref>B6:B100 B2:B4</xm:sqref>
+          <xm:sqref>B11:B105 B2:B4</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2413,22 +2737,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981CFA5E-60F3-446F-A856-2FA65B76879A}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.81640625" customWidth="1"/>
-    <col min="8" max="8" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.1796875" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -2463,7 +2787,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -2518,72 +2842,72 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DC79B9-9C58-497E-9FD8-D3F2239E9BDC}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>77</v>
       </c>

--- a/Spine_Projects/01_input_data/01_input_raw/Products/hydrogen/Model_Data_Base_hydrogen.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/hydrogen/Model_Data_Base_hydrogen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7EAECE5-810D-4BEF-BA0F-CAD7C228B195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3D4A49-114D-44F8-BEA2-80D001EDE81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="106">
   <si>
     <t>Unit</t>
   </si>
@@ -298,21 +298,9 @@
     <t>initial_units_on</t>
   </si>
   <si>
-    <t>heat_low</t>
-  </si>
-  <si>
-    <t>heat_high</t>
-  </si>
-  <si>
-    <t>heat_split</t>
-  </si>
-  <si>
     <t>Auxilliary</t>
   </si>
   <si>
-    <t>internal_heat</t>
-  </si>
-  <si>
     <t>Input3</t>
   </si>
   <si>
@@ -398,6 +386,12 @@
   </si>
   <si>
     <t>pl_wind_offshore_PPA</t>
+  </si>
+  <si>
+    <t>excess_heat</t>
+  </si>
+  <si>
+    <t>heat</t>
   </si>
 </sst>
 </file>
@@ -447,7 +441,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -475,20 +469,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -499,16 +484,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -519,9 +503,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1230,8 +1211,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}" name="Table1" displayName="Table1" ref="A1:R12" totalsRowShown="0">
-  <autoFilter ref="A1:R12" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}" name="Table1" displayName="Table1" ref="A1:R10" totalsRowShown="0">
+  <autoFilter ref="A1:R10" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{C73E51D0-1842-42F3-9C00-F0DBD2E661BE}" name="Unit"/>
     <tableColumn id="40" xr3:uid="{C2CFC5A4-5329-4F74-926A-18CEB18C062C}" name="Object_type"/>
@@ -1257,8 +1238,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}" name="Table5" displayName="Table5" ref="A1:Q12" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:Q12" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}" name="Table5" displayName="Table5" ref="A1:Q11" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:Q11" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{2BE3E317-773B-4E82-9035-69A43C6CB21B}" name="Unit" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{22613EE0-390D-4B04-9A9B-6D5554D1C8ED}" name="Object_type" dataDxfId="18"/>
@@ -1292,7 +1273,7 @@
     <tableColumn id="3" xr3:uid="{0B221EED-10BC-4C34-AC5E-37A826B1E8AE}" name="Input2"/>
     <tableColumn id="4" xr3:uid="{13095F0A-BCF6-40A3-B029-60B11214B154}" name="Output1"/>
     <tableColumn id="5" xr3:uid="{4C6B3E52-C4A2-4D67-B50B-9DAA089E0399}" name="Output2"/>
-    <tableColumn id="22" xr3:uid="{551A8663-4680-4147-9E64-4B9A8EA76642}" name="Connection_type" dataDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{551A8663-4680-4147-9E64-4B9A8EA76642}" name="Connection_type" dataDxfId="2"/>
     <tableColumn id="6" xr3:uid="{5DF4D35D-AD4C-4648-BC90-B2BA8F975A09}" name="Cap_Input1_existing"/>
     <tableColumn id="15" xr3:uid="{C0BCA9EF-0E20-40E5-9820-0EA6AB1DE457}" name="Cap_Input1_max"/>
     <tableColumn id="14" xr3:uid="{D4F16D16-99DE-47DA-B08A-6DD56FEBC7A4}" name="Cap_Input2_existing"/>
@@ -1311,7 +1292,7 @@
     <tableColumn id="21" xr3:uid="{EC2CC790-C17D-4744-A981-3984808E5B33}" name="vom_cost_Input2"/>
     <tableColumn id="24" xr3:uid="{41B338E4-2058-41E9-8000-97D77450FBC3}" name="vom_cost_Output1"/>
     <tableColumn id="25" xr3:uid="{DDAFCF0A-1EF1-4B7B-9742-01F9FA7A22E5}" name="vom_cost_Output2"/>
-    <tableColumn id="29" xr3:uid="{79DE3A19-CED6-47DE-AEF5-F6BB2D320F24}" name="connection_investment_tech_lifetime" dataDxfId="0"/>
+    <tableColumn id="29" xr3:uid="{79DE3A19-CED6-47DE-AEF5-F6BB2D320F24}" name="connection_investment_tech_lifetime" dataDxfId="1"/>
     <tableColumn id="30" xr3:uid="{09434E4A-7BF5-4547-9708-EA3F0F7ADC8E}" name="initial_connections_invested_available"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1322,7 +1303,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}" name="Table134" displayName="Table134" ref="A1:K5" totalsRowShown="0">
   <autoFilter ref="A1:K5" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="0">
       <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Connections!A2:A105,ISNUMBER(FIND("storage",Connections!A2:A105)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{8C29206C-8DC6-44DB-A8D1-3D5625C277AD}" name="Object_type"/>
@@ -1647,12 +1628,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="18" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" customWidth="1"/>
+    <col min="18" max="18" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -1663,7 +1659,7 @@
         <v>41</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
@@ -1672,16 +1668,16 @@
         <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="J1" t="s">
         <v>58</v>
@@ -1719,33 +1715,33 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -1774,10 +1770,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
         <v>68</v>
@@ -1786,17 +1782,8 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
       <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
+      <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P8" s="1"/>
@@ -1804,20 +1791,12 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P9" s="1"/>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
+      <c r="Q9" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P11" xr:uid="{D92CB468-B7A9-4082-9B81-D3B4634F286E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P9" xr:uid="{D92CB468-B7A9-4082-9B81-D3B4634F286E}">
       <formula1>"h, D, W, M, Q, Y"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1833,7 +1812,7 @@
           <x14:formula1>
             <xm:f>Drop_Down!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>B13:B1048576 B1:B11</xm:sqref>
+          <xm:sqref>B11:B1048576 B1:B9</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1843,12 +1822,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CABA7C5-6230-4207-9D35-0A95D86E66AC}">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="7" max="8" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1865,10 +1851,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>3</v>
@@ -1877,31 +1863,31 @@
         <v>4</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -1916,22 +1902,22 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -1941,7 +1927,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -1956,7 +1942,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -1966,7 +1952,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -1998,7 +1984,7 @@
         <v>69</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -2015,73 +2001,57 @@
       <c r="Q5" s="4"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H6" s="6" t="s">
+      <c r="A6" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>74</v>
       </c>
+      <c r="C6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" s="3"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6">
+      <c r="N6" s="6">
         <v>1</v>
       </c>
+      <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>98</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
-      <c r="N7" s="4">
-        <v>1</v>
-      </c>
+      <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -2112,24 +2082,40 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2144,7 +2130,7 @@
           <x14:formula1>
             <xm:f>Drop_Down!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>B12 B1:B9</xm:sqref>
+          <xm:sqref>B11 B1:B8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2154,31 +2140,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C870BDA0-9E4C-481D-87BE-9D47789809C8}">
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" customWidth="1"/>
-    <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
-    <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.85546875" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" customWidth="1"/>
-    <col min="22" max="23" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="38.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
@@ -2387,7 +2374,7 @@
         <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
         <v>67</v>
@@ -2419,7 +2406,7 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -2428,10 +2415,10 @@
         <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -2478,13 +2465,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s">
         <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>63</v>
@@ -2516,7 +2503,7 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
         <v>48</v>
@@ -2525,10 +2512,10 @@
         <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
@@ -2575,13 +2562,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s">
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
@@ -2613,7 +2600,7 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s">
         <v>48</v>
@@ -2622,10 +2609,10 @@
         <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
@@ -2672,13 +2659,13 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s">
         <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
         <v>63</v>
@@ -2707,10 +2694,6 @@
       <c r="AA10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="G11" s="9"/>
-      <c r="Z11" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2909,7 +2892,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Spine_Projects/01_input_data/01_input_raw/Products/hydrogen/Model_Data_Base_hydrogen.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/hydrogen/Model_Data_Base_hydrogen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\hydrogen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3D4A49-114D-44F8-BEA2-80D001EDE81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1EDF1C-A9A1-4C7D-A0B3-8EBF44945192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="-10110" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" concurrentManualCount="6"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="103">
   <si>
     <t>Unit</t>
   </si>
@@ -274,12 +274,6 @@
     <t>power_wholesale</t>
   </si>
   <si>
-    <t>pl_dh</t>
-  </si>
-  <si>
-    <t>dh</t>
-  </si>
-  <si>
     <t>water</t>
   </si>
   <si>
@@ -389,9 +383,6 @@
   </si>
   <si>
     <t>excess_heat</t>
-  </si>
-  <si>
-    <t>heat</t>
   </si>
 </sst>
 </file>
@@ -1264,8 +1255,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA11" totalsRowShown="0">
-  <autoFilter ref="A1:AA11" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA10" totalsRowShown="0">
+  <autoFilter ref="A1:AA10" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{26B0CA71-1EA9-44CF-8E6D-31054ECA99A6}" name="Connection"/>
     <tableColumn id="26" xr3:uid="{E67F4435-EF76-417C-B715-53719E5FB41F}" name="Object_type"/>
@@ -1304,7 +1295,7 @@
   <autoFilter ref="A1:K5" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="0">
-      <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Connections!A2:A105,ISNUMBER(FIND("storage",Connections!A2:A105)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Connections!A2:A104,ISNUMBER(FIND("storage",Connections!A2:A104)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{8C29206C-8DC6-44DB-A8D1-3D5625C277AD}" name="Object_type"/>
     <tableColumn id="4" xr3:uid="{AEAA1B51-84C1-491F-81D5-7757B30BDCCD}" name="value_before"/>
@@ -1629,29 +1620,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
   <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" customWidth="1"/>
-    <col min="18" max="18" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" customWidth="1"/>
+    <col min="18" max="18" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1659,7 +1650,7 @@
         <v>41</v>
       </c>
       <c r="C1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
@@ -1668,16 +1659,16 @@
         <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J1" t="s">
         <v>58</v>
@@ -1704,10 +1695,10 @@
         <v>40</v>
       </c>
       <c r="R1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -1715,40 +1706,40 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -1768,28 +1759,28 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="P7" s="1"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
@@ -1823,21 +1814,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CABA7C5-6230-4207-9D35-0A95D86E66AC}">
   <dimension ref="A1:Q11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1851,10 +1842,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>3</v>
@@ -1863,34 +1854,34 @@
         <v>4</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="P1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>62</v>
       </c>
@@ -1902,7 +1893,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6"/>
@@ -1915,9 +1906,9 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -1927,7 +1918,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -1940,9 +1931,9 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -1952,7 +1943,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -1965,9 +1956,9 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>54</v>
@@ -1976,15 +1967,15 @@
         <v>63</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -2000,21 +1991,21 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="6"/>
@@ -2029,7 +2020,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2047,7 +2038,7 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -2063,7 +2054,7 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2082,7 +2073,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -2098,7 +2089,7 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2140,35 +2131,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C870BDA0-9E4C-481D-87BE-9D47789809C8}">
-  <dimension ref="A1:AA10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AA9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="38.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -2251,7 +2242,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -2310,24 +2301,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G3" t="s">
         <v>31</v>
@@ -2366,18 +2357,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>93</v>
+      </c>
+      <c r="F4" t="s">
+        <v>65</v>
       </c>
       <c r="G4" t="s">
         <v>31</v>
@@ -2388,11 +2385,26 @@
       <c r="I4">
         <v>1000</v>
       </c>
+      <c r="J4">
+        <v>1000</v>
+      </c>
+      <c r="K4">
+        <v>1000</v>
+      </c>
       <c r="L4">
         <v>1000</v>
       </c>
       <c r="M4">
         <v>1000</v>
+      </c>
+      <c r="N4">
+        <v>1000</v>
+      </c>
+      <c r="O4">
+        <v>1000</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
       </c>
       <c r="T4">
         <v>1</v>
@@ -2404,24 +2416,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
         <v>31</v>
@@ -2432,26 +2438,11 @@
       <c r="I5">
         <v>1000</v>
       </c>
-      <c r="J5">
-        <v>1000</v>
-      </c>
-      <c r="K5">
-        <v>1000</v>
-      </c>
       <c r="L5">
         <v>1000</v>
       </c>
       <c r="M5">
         <v>1000</v>
-      </c>
-      <c r="N5">
-        <v>1000</v>
-      </c>
-      <c r="O5">
-        <v>1000</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
       </c>
       <c r="T5">
         <v>1</v>
@@ -2463,18 +2454,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s">
         <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>65</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>94</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
@@ -2485,11 +2482,26 @@
       <c r="I6">
         <v>1000</v>
       </c>
+      <c r="J6">
+        <v>1000</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
       <c r="L6">
         <v>1000</v>
       </c>
       <c r="M6">
         <v>1000</v>
+      </c>
+      <c r="N6">
+        <v>1000</v>
+      </c>
+      <c r="O6">
+        <v>1000</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
       </c>
       <c r="T6">
         <v>1</v>
@@ -2501,24 +2513,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
         <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
         <v>31</v>
@@ -2529,26 +2535,11 @@
       <c r="I7">
         <v>1000</v>
       </c>
-      <c r="J7">
-        <v>1000</v>
-      </c>
-      <c r="K7">
-        <v>1000</v>
-      </c>
       <c r="L7">
         <v>1000</v>
       </c>
       <c r="M7">
         <v>1000</v>
-      </c>
-      <c r="N7">
-        <v>1000</v>
-      </c>
-      <c r="O7">
-        <v>1000</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
       </c>
       <c r="T7">
         <v>1</v>
@@ -2560,18 +2551,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>95</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
       </c>
       <c r="G8" t="s">
         <v>31</v>
@@ -2582,11 +2579,26 @@
       <c r="I8">
         <v>1000</v>
       </c>
+      <c r="J8">
+        <v>1000</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
+      </c>
       <c r="L8">
         <v>1000</v>
       </c>
       <c r="M8">
         <v>1000</v>
+      </c>
+      <c r="N8">
+        <v>1000</v>
+      </c>
+      <c r="O8">
+        <v>1000</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
       </c>
       <c r="T8">
         <v>1</v>
@@ -2598,24 +2610,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
         <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
         <v>31</v>
@@ -2626,26 +2632,11 @@
       <c r="I9">
         <v>1000</v>
       </c>
-      <c r="J9">
-        <v>1000</v>
-      </c>
-      <c r="K9">
-        <v>1000</v>
-      </c>
       <c r="L9">
         <v>1000</v>
       </c>
       <c r="M9">
         <v>1000</v>
-      </c>
-      <c r="N9">
-        <v>1000</v>
-      </c>
-      <c r="O9">
-        <v>1000</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
       </c>
       <c r="T9">
         <v>1</v>
@@ -2654,44 +2645,6 @@
         <v>52</v>
       </c>
       <c r="AA9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10">
-        <v>1000</v>
-      </c>
-      <c r="I10">
-        <v>1000</v>
-      </c>
-      <c r="L10">
-        <v>1000</v>
-      </c>
-      <c r="M10">
-        <v>1000</v>
-      </c>
-      <c r="T10">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA10">
         <v>1</v>
       </c>
     </row>
@@ -2709,7 +2662,7 @@
           <x14:formula1>
             <xm:f>Drop_Down!$A$2:$A$60</xm:f>
           </x14:formula1>
-          <xm:sqref>B11:B105 B2:B4</xm:sqref>
+          <xm:sqref>B10:B104 B2:B3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2720,22 +2673,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981CFA5E-60F3-446F-A856-2FA65B76879A}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -2770,9 +2723,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
         <v>44</v>
@@ -2825,74 +2778,74 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DC79B9-9C58-497E-9FD8-D3F2239E9BDC}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
